--- a/data/trans_orig/IP3109_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Clase-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>90676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181313</t>
+          <t>181036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72816</t>
+          <t>73311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>78068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153601</t>
+          <t>153814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158389</t>
+          <t>158396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60220</t>
+          <t>60593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157074</t>
+          <t>156559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182022</t>
+          <t>181431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369261</t>
+          <t>369129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>94464</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113420</t>
+          <t>113973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210960</t>
+          <t>210698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61241</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131193</t>
+          <t>131184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>583084</t>
+          <t>584069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>590557</t>
+          <t>590571</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>629206</t>
+          <t>629119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1214777</t>
+          <t>1216163</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1224334</t>
+          <t>1224536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76459</t>
+          <t>76864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83328</t>
+          <t>83325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76060</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155366</t>
+          <t>154914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80701</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170730</t>
+          <t>170733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76524</t>
+          <t>76216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155186</t>
+          <t>154831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173045</t>
+          <t>173545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179113</t>
+          <t>179046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198792</t>
+          <t>198717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>374825</t>
+          <t>375751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383425</t>
+          <t>383577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132790</t>
+          <t>133010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>124066</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128963</t>
+          <t>128961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259887</t>
+          <t>258980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266182</t>
+          <t>266233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45893</t>
+          <t>45650</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62597</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110102</t>
+          <t>110054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>599090</t>
+          <t>599067</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>609299</t>
+          <t>609344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>637683</t>
+          <t>637712</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>645428</t>
+          <t>645554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1240345</t>
+          <t>1239940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1253187</t>
+          <t>1253014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80565</t>
+          <t>80435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153258</t>
+          <t>153123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>158209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87447</t>
+          <t>87403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189075</t>
+          <t>189552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65138</t>
+          <t>64916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>121756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>195642</t>
+          <t>195395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201752</t>
+          <t>201758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>391278</t>
+          <t>391360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397485</t>
+          <t>397623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123677</t>
+          <t>123716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129282</t>
+          <t>129267</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129349</t>
+          <t>129463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>256041</t>
+          <t>256315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262394</t>
+          <t>262684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>115350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>595470</t>
+          <t>595623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>605236</t>
+          <t>604768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>641884</t>
+          <t>641654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>648413</t>
+          <t>648294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1240524</t>
+          <t>1240586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1251598</t>
+          <t>1251755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74743</t>
+          <t>75576</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88474</t>
+          <t>88179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114994</t>
+          <t>115306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127540</t>
+          <t>127572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194929</t>
+          <t>194409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213749</t>
+          <t>213125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26966</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41957</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73838</t>
+          <t>74032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85250</t>
+          <t>85036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69747</t>
+          <t>69865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82841</t>
+          <t>82465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148973</t>
+          <t>148417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165449</t>
+          <t>165582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23961</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39686</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81917</t>
+          <t>81721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97389</t>
+          <t>98131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>180187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199102</t>
+          <t>199586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174765</t>
+          <t>175138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193216</t>
+          <t>193645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361400</t>
+          <t>359819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386887</t>
+          <t>388132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>37520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>39239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>67552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92342</t>
+          <t>92206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104720</t>
+          <t>104550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117598</t>
+          <t>117837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137771</t>
+          <t>138512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214545</t>
+          <t>216268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>237349</t>
+          <t>238328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21125</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>41059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59860</t>
+          <t>58137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55444</t>
+          <t>56224</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64879</t>
+          <t>64694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53849</t>
+          <t>54115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63494</t>
+          <t>63785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112714</t>
+          <t>113085</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126222</t>
+          <t>126314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>539038</t>
+          <t>540150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571884</t>
+          <t>572500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>599787</t>
+          <t>602753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>635340</t>
+          <t>638664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1151459</t>
+          <t>1151944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1199979</t>
+          <t>1201371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72422</t>
+          <t>71806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105268</t>
+          <t>104156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96463</t>
+          <t>93139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132016</t>
+          <t>129050</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176131</t>
+          <t>174739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>224651</t>
+          <t>224166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
